--- a/public/reports/HDFCBANK_NS_Financial_Model.xlsx
+++ b/public/reports/HDFCBANK_NS_Financial_Model.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="615">
   <si>
     <t>HDFC Bank Limited (HDFCBANK.NS)</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Fair value per share (INR)</t>
   </si>
   <si>
-    <t>Upside / (downside)</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited)</t>
   </si>
   <si>
     <t>Primary method</t>
@@ -74,7 +74,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Commercial Banking Institution valued via RESIDUAL_INCOME_PB. 54/54 accounting invariants passed; reasonableness verdict ECONOMICALLY_SOUND.</t>
+    <t>Commercial Banking Institution valued via RESIDUAL_INCOME_PB. 54/54 accounting invariants passed; reasonableness assessment ECONOMICALLY_SOUND.</t>
   </si>
   <si>
     <t>KEY FINANCIALS (₹ Crores)</t>
@@ -188,19 +188,19 @@
     <t>Snapshot ID</t>
   </si>
   <si>
-    <t>snap_HDFCBANK_NS_ff054d29d13d</t>
+    <t>snap_HDFCBANK_NS_f8cc0c05eedf</t>
   </si>
   <si>
     <t>Snapshot SHA-256</t>
   </si>
   <si>
-    <t>ff054d29d13dddfc9d2e1136cddc4dc83b2eaa2d80ee6e8af71d39c722fe5784</t>
+    <t>f8cc0c05eedfcecf85ce8d847cff6d3d65cf2b31b44fb04119c67aa8b0c9a29d</t>
   </si>
   <si>
     <t>Built at</t>
   </si>
   <si>
-    <t>2026-11-01T14:57:59.137Z</t>
+    <t>2026-11-01T15:04:10.906Z</t>
   </si>
   <si>
     <t>Analysis status</t>
@@ -272,7 +272,7 @@
     <t>420.32</t>
   </si>
   <si>
-    <t>Upside / (downside) %</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited) %</t>
   </si>
   <si>
     <t>-39.33</t>
@@ -758,7 +758,7 @@
     <t>withheld</t>
   </si>
   <si>
-    <t>Not eligible by methodology: valuation methodology routes this archetype (BANK) to RESIDUAL_INCOME_PB and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF stance is published.</t>
+    <t>Not eligible by methodology: valuation methodology routes this archetype (BANK) to RESIDUAL_INCOME_PB and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF reading is published.</t>
   </si>
   <si>
     <t>Segment analysis</t>
@@ -905,7 +905,7 @@
     <t>Peer statistics are computed from the same provider extractor for the subject and every peer; see the Peers sheet for the statistic definition.</t>
   </si>
   <si>
-    <t>Withheld: DCF cross-check -- Not eligible by methodology: valuation methodology routes this archetype (BANK) to RESIDUAL_INCOME_PB and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF stance is published.</t>
+    <t>Withheld: DCF cross-check -- Not eligible by methodology: valuation methodology routes this archetype (BANK) to RESIDUAL_INCOME_PB and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF reading is published.</t>
   </si>
   <si>
     <t>Withheld: Segment analysis -- no Ind AS 108 segment disclosure was read for this issuer and the provider published no split</t>
@@ -1103,7 +1103,7 @@
     <t>Forensic audit complete: Overall Health: UNAVAILABLE | Altman Z: N/A (N/A) | Piotroski F: N/A/9 | Beneish M: N/A (N/A).</t>
   </si>
   <si>
-    <t>ACCOUNTING QUALITY (verdict UNAVAILABLE)</t>
+    <t>ACCOUNTING QUALITY (assessment UNAVAILABLE)</t>
   </si>
   <si>
     <t>Check</t>
@@ -1583,40 +1583,19 @@
     <t>Assumptions hash (12)</t>
   </si>
   <si>
-    <t>snap_HDFCBANK_NS_ff054d29d13d  &lt;- THIS WORKBOOK</t>
+    <t>snap_HDFCBANK_NS_f8cc0c05eedf  &lt;- THIS WORKBOOK</t>
+  </si>
+  <si>
+    <t>2026-11-01T15:03:26.167Z</t>
   </si>
   <si>
     <t>74234e98afe7</t>
   </si>
   <si>
-    <t>snap_HDFCBANK_NS_c17e6b2cbffe</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:57:59.049Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCBANK_NS_5ad9eb62a347</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:55:59.931Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCBANK_NS_40a45718408b</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:55:59.818Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCBANK_NS_241a207c6b4b</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:52:21.257Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCBANK_NS_0df2a09d7a3f</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:52:21.156Z</t>
+    <t>snap_HDFCBANK_NS_0157a3d062ef</t>
+  </si>
+  <si>
+    <t>2026-11-01T15:03:26.080Z</t>
   </si>
   <si>
     <t>OVERRIDES APPLIED TO THIS WORKBOOK</t>
@@ -1811,13 +1790,13 @@
     <t>a funding shortfall is withheld by the model, not published as negative borrowings or negative liquidity</t>
   </si>
   <si>
-    <t>No DCF stance without a DCF</t>
+    <t>No DCF reading without a DCF</t>
   </si>
   <si>
     <t>VALUATION</t>
   </si>
   <si>
-    <t>no DCF ran and no stance is published</t>
+    <t>no DCF ran and no reading is published</t>
   </si>
   <si>
     <t>No bonus / split is classified as economic dilution</t>
@@ -1889,7 +1868,7 @@
     <t>SAVED RECORD AND VERIFIER RECEIPTS</t>
   </si>
   <si>
-    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_HDFCBANK_NS_ff054d29d13d/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
+    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_HDFCBANK_NS_f8cc0c05eedf/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
   </si>
   <si>
     <t>Chart data (editable)</t>
@@ -7999,7 +7978,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
@@ -8065,7 +8044,7 @@
         <v>514</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>515</v>
       </c>
       <c r="C6" s="14">
         <v>692.8</v>
@@ -8086,15 +8065,15 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C7" s="14">
         <v>692.8</v>
@@ -8117,211 +8096,87 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>518</v>
-      </c>
-      <c r="B8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C8" s="14">
-        <v>692.8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="14">
-        <v>420.32</v>
-      </c>
-      <c r="G8" s="14">
-        <f>F8-420.32</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="34">
-        <f>G8/420.32</f>
-        <v>0</v>
-      </c>
-      <c r="I8" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>520</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="C9" s="14">
-        <v>692.8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="14">
-        <v>420.32</v>
-      </c>
-      <c r="G9" s="14">
-        <f>F9-420.32</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="34">
-        <f>G9/420.32</f>
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>522</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B13" t="s">
         <v>523</v>
       </c>
-      <c r="C10" s="14">
-        <v>692.8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="14">
-        <v>420.32</v>
-      </c>
-      <c r="G10" s="14">
-        <f>F10-420.32</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="34">
-        <f>G10/420.32</f>
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C13" t="s">
         <v>524</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>525</v>
       </c>
-      <c r="C11" s="14">
-        <v>692.8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="14">
-        <v>420.32</v>
-      </c>
-      <c r="G11" s="14">
-        <f>F11-420.32</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="34">
-        <f>G11/420.32</f>
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B14" t="s">
         <v>526</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C14" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>522</v>
+      </c>
+      <c r="B15" t="s">
         <v>528</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C15" t="s">
         <v>529</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>522</v>
+      </c>
+      <c r="B16" t="s">
         <v>530</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C16" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="B18" t="s">
-        <v>533</v>
-      </c>
-      <c r="C18" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>529</v>
-      </c>
-      <c r="B19" t="s">
-        <v>535</v>
-      </c>
-      <c r="C19" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>529</v>
-      </c>
-      <c r="B20" t="s">
-        <v>537</v>
-      </c>
-      <c r="C20" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -8346,17 +8201,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -8368,7 +8223,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>444</v>
@@ -8380,27 +8235,27 @@
         <v>174</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>503</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="B6" t="s">
         <v>452</v>
@@ -8409,19 +8264,19 @@
         <v>407994.8</v>
       </c>
       <c r="D6" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E6" t="s">
         <v>292</v>
       </c>
       <c r="F6" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G6" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="H6" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="I6" t="s">
         <v>24</v>
@@ -8432,7 +8287,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B7" t="s">
         <v>452</v>
@@ -8441,19 +8296,19 @@
         <v>64062</v>
       </c>
       <c r="D7" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E7" t="s">
         <v>292</v>
       </c>
       <c r="F7" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G7" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="H7" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="I7" t="s">
         <v>24</v>
@@ -8464,7 +8319,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B8" t="s">
         <v>481</v>
@@ -8473,19 +8328,19 @@
         <v>470915.9</v>
       </c>
       <c r="D8" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E8" t="s">
         <v>292</v>
       </c>
       <c r="F8" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G8" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="H8" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="I8" t="s">
         <v>24</v>
@@ -8496,7 +8351,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B9" t="s">
         <v>481</v>
@@ -8505,19 +8360,19 @@
         <v>68144.3</v>
       </c>
       <c r="D9" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E9" t="s">
         <v>292</v>
       </c>
       <c r="F9" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G9" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="H9" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="I9" t="s">
         <v>24</v>
@@ -8528,7 +8383,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="B10" t="s">
         <v>489</v>
@@ -8537,19 +8392,19 @@
         <v>495462.9</v>
       </c>
       <c r="D10" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E10" t="s">
         <v>292</v>
       </c>
       <c r="F10" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G10" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="H10" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="I10" t="s">
         <v>24</v>
@@ -8560,7 +8415,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B11" t="s">
         <v>489</v>
@@ -8569,19 +8424,19 @@
         <v>76026</v>
       </c>
       <c r="D11" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E11" t="s">
         <v>292</v>
       </c>
       <c r="F11" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G11" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="H11" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="I11" t="s">
         <v>24</v>
@@ -8592,7 +8447,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -8607,19 +8462,19 @@
         <v>355</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>359</v>
@@ -8627,13 +8482,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B15" t="s">
         <v>295</v>
       </c>
       <c r="C15" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -8645,18 +8500,18 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B16" t="s">
         <v>295</v>
       </c>
       <c r="C16" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -8668,18 +8523,18 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B17" t="s">
         <v>295</v>
       </c>
       <c r="C17" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -8691,18 +8546,18 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="B18" t="s">
         <v>295</v>
       </c>
       <c r="C18" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -8714,18 +8569,18 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B19" t="s">
         <v>295</v>
       </c>
       <c r="C19" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -8737,18 +8592,18 @@
         <v>4.656612873077393e-10</v>
       </c>
       <c r="G19" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="B20" t="s">
         <v>295</v>
       </c>
       <c r="C20" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -8760,18 +8615,18 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B21" t="s">
         <v>295</v>
       </c>
       <c r="C21" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
@@ -8783,18 +8638,18 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B22" t="s">
         <v>295</v>
       </c>
       <c r="C22" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -8806,18 +8661,18 @@
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="B23" t="s">
         <v>295</v>
       </c>
       <c r="C23" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -8829,18 +8684,18 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B24" t="s">
         <v>295</v>
       </c>
       <c r="C24" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -8852,18 +8707,18 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B25" t="s">
         <v>295</v>
       </c>
       <c r="C25" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -8875,18 +8730,18 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B26" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C26" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -8898,18 +8753,18 @@
         <v>24</v>
       </c>
       <c r="G26" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B27" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="C27" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -8921,18 +8776,18 @@
         <v>24</v>
       </c>
       <c r="G27" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="B28" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="C28" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -8944,12 +8799,12 @@
         <v>24</v>
       </c>
       <c r="G28" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -8961,41 +8816,41 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="B32" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="C32" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="D32" t="s">
         <v>247</v>
       </c>
       <c r="E32" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -9007,10 +8862,10 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B35" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -9039,10 +8894,10 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="B39" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -9055,7 +8910,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="B41" t="s">
         <v>230</v>
@@ -9063,7 +8918,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="B42" t="s">
         <v>237</v>
@@ -9074,7 +8929,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="B43" t="s">
         <v>240</v>
@@ -9085,7 +8940,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="B44" t="s">
         <v>242</v>
@@ -9096,7 +8951,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -9108,7 +8963,7 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -9128,17 +8983,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -9148,12 +9003,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
